--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fake-paper" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$N$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$N$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$N$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$N$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$N$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$N$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$N$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$N$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$N$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2857,8 +2857,386 @@
         <v>0</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>56</v>
+      </c>
+      <c r="C47" t="n">
+        <v>175126</v>
+      </c>
+      <c r="D47" t="n">
+        <v>185</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>15</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>57</v>
+      </c>
+      <c r="C48" t="n">
+        <v>175948</v>
+      </c>
+      <c r="D48" t="n">
+        <v>186</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>15</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>59</v>
+      </c>
+      <c r="C49" t="n">
+        <v>176827</v>
+      </c>
+      <c r="D49" t="n">
+        <v>188</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>15</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>61</v>
+      </c>
+      <c r="C50" t="n">
+        <v>178695</v>
+      </c>
+      <c r="D50" t="n">
+        <v>190</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>15</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>61</v>
+      </c>
+      <c r="C51" t="n">
+        <v>179568</v>
+      </c>
+      <c r="D51" t="n">
+        <v>191</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>15</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>61</v>
+      </c>
+      <c r="C52" t="n">
+        <v>182425</v>
+      </c>
+      <c r="D52" t="n">
+        <v>193</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>15</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>62</v>
+      </c>
+      <c r="C53" t="n">
+        <v>182623</v>
+      </c>
+      <c r="D53" t="n">
+        <v>194</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>15</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N46"/>
+  <autoFilter ref="A1:N53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2869,7 +3247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5288,8 +5666,386 @@
         <v>0</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>135</v>
+      </c>
+      <c r="C47" t="n">
+        <v>138125</v>
+      </c>
+      <c r="D47" t="n">
+        <v>157</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>15</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>136</v>
+      </c>
+      <c r="C48" t="n">
+        <v>138587</v>
+      </c>
+      <c r="D48" t="n">
+        <v>159</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>15</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>137</v>
+      </c>
+      <c r="C49" t="n">
+        <v>140463</v>
+      </c>
+      <c r="D49" t="n">
+        <v>161</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>15</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>140</v>
+      </c>
+      <c r="C50" t="n">
+        <v>142569</v>
+      </c>
+      <c r="D50" t="n">
+        <v>164</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>15</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>141</v>
+      </c>
+      <c r="C51" t="n">
+        <v>144530</v>
+      </c>
+      <c r="D51" t="n">
+        <v>166</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>15</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>141</v>
+      </c>
+      <c r="C52" t="n">
+        <v>147102</v>
+      </c>
+      <c r="D52" t="n">
+        <v>168</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>15</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>144</v>
+      </c>
+      <c r="C53" t="n">
+        <v>147661</v>
+      </c>
+      <c r="D53" t="n">
+        <v>170</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>15</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N46"/>
+  <autoFilter ref="A1:N53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5300,7 +6056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6505,7 +7261,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
         <v>5</v>
       </c>
@@ -6523,8 +7278,352 @@
         <v>0</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" t="n">
+        <v>40778</v>
+      </c>
+      <c r="D26" t="n">
+        <v>30</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>13</v>
+      </c>
+      <c r="C27" t="n">
+        <v>41614</v>
+      </c>
+      <c r="D27" t="n">
+        <v>31</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>14</v>
+      </c>
+      <c r="C28" t="n">
+        <v>42598</v>
+      </c>
+      <c r="D28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>6</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>14</v>
+      </c>
+      <c r="C29" t="n">
+        <v>44481</v>
+      </c>
+      <c r="D29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D30" t="n">
+        <v>36</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>14</v>
+      </c>
+      <c r="C31" t="n">
+        <v>47413</v>
+      </c>
+      <c r="D31" t="n">
+        <v>38</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>7</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>14</v>
+      </c>
+      <c r="C32" t="n">
+        <v>47485</v>
+      </c>
+      <c r="D32" t="n">
+        <v>39</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>9</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N25"/>
+  <autoFilter ref="A1:N32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6535,7 +7634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7740,7 +8839,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
         <v>4</v>
       </c>
@@ -7758,8 +8856,352 @@
         <v>1</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" t="n">
+        <v>36619</v>
+      </c>
+      <c r="D26" t="n">
+        <v>30</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" t="n">
+        <v>37518</v>
+      </c>
+      <c r="D27" t="n">
+        <v>31</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>11</v>
+      </c>
+      <c r="C28" t="n">
+        <v>38276</v>
+      </c>
+      <c r="D28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" t="n">
+        <v>39305</v>
+      </c>
+      <c r="D29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>13</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>11</v>
+      </c>
+      <c r="C30" t="n">
+        <v>39861</v>
+      </c>
+      <c r="D30" t="n">
+        <v>36</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>14</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" t="n">
+        <v>41912</v>
+      </c>
+      <c r="D31" t="n">
+        <v>37</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>15</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C32" t="n">
+        <v>42085</v>
+      </c>
+      <c r="D32" t="n">
+        <v>38</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>15</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N25"/>
+  <autoFilter ref="A1:N32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7770,7 +9212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8512,7 +9954,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
         <v>4</v>
       </c>
@@ -8530,8 +9971,352 @@
         <v>1</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>24859</v>
+      </c>
+      <c r="D16" t="n">
+        <v>26</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>25801</v>
+      </c>
+      <c r="D17" t="n">
+        <v>27</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>26871</v>
+      </c>
+      <c r="D18" t="n">
+        <v>29</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>28680</v>
+      </c>
+      <c r="D19" t="n">
+        <v>31</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>29636</v>
+      </c>
+      <c r="D20" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>32415</v>
+      </c>
+      <c r="D21" t="n">
+        <v>34</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" t="n">
+        <v>32646</v>
+      </c>
+      <c r="D22" t="n">
+        <v>35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N15"/>
+  <autoFilter ref="A1:N22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8542,7 +10327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8798,7 +10583,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>0</v>
       </c>
@@ -8816,8 +10600,334 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1099</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1099</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1099</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2252</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4178</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N5"/>
+  <autoFilter ref="A1:N12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -21,18 +21,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="company-facts" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$N$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$N$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$N$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$N$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$N$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$N$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$N$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$N$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$N$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$N$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$N$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3292,8 +3292,107 @@
         <v>0</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>15</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>63</v>
+      </c>
+      <c r="C56" t="n">
+        <v>183565</v>
+      </c>
+      <c r="D56" t="n">
+        <v>195</v>
+      </c>
+      <c r="E56" t="n">
+        <v>40</v>
+      </c>
+      <c r="F56" t="n">
+        <v>872.3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>941</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>15</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N54"/>
+  <autoFilter ref="A1:N56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3304,7 +3403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3413,8 +3512,6 @@
       <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
@@ -3432,8 +3529,93 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>18330</v>
+      </c>
+      <c r="D4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>989</v>
+      </c>
+      <c r="G4" t="n">
+        <v>989</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3444,7 +3626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3558,7 +3740,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
@@ -3576,8 +3757,98 @@
         <v>2</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>29029</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3752.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1230</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3588,7 +3859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3702,7 +3973,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
@@ -3720,8 +3990,98 @@
         <v>2</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C4" t="n">
+        <v>37336</v>
+      </c>
+      <c r="D4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1412</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1235</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3732,7 +4092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6574,8 +6934,107 @@
         <v>0</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>15</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>148</v>
+      </c>
+      <c r="C56" t="n">
+        <v>150413</v>
+      </c>
+      <c r="D56" t="n">
+        <v>173</v>
+      </c>
+      <c r="E56" t="n">
+        <v>46</v>
+      </c>
+      <c r="F56" t="n">
+        <v>768</v>
+      </c>
+      <c r="G56" t="n">
+        <v>867</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>15</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N54"/>
+  <autoFilter ref="A1:N56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6586,7 +7045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8174,7 +8633,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
         <v>9</v>
       </c>
@@ -8192,8 +8650,98 @@
         <v>2</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>9</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>15</v>
+      </c>
+      <c r="C35" t="n">
+        <v>48808</v>
+      </c>
+      <c r="D35" t="n">
+        <v>40</v>
+      </c>
+      <c r="E35" t="n">
+        <v>30</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1147.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1061</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>9</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N33"/>
+  <autoFilter ref="A1:N35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8204,7 +8752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9792,7 +10340,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
         <v>15</v>
       </c>
@@ -9810,8 +10357,98 @@
         <v>1</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>15</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>12</v>
+      </c>
+      <c r="C35" t="n">
+        <v>42439</v>
+      </c>
+      <c r="D35" t="n">
+        <v>39</v>
+      </c>
+      <c r="E35" t="n">
+        <v>30</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1088.3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1021</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>15</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N33"/>
+  <autoFilter ref="A1:N35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9822,7 +10459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10947,7 +11584,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
         <v>5</v>
       </c>
@@ -10965,8 +11601,98 @@
         <v>0</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>34597</v>
+      </c>
+      <c r="D25" t="n">
+        <v>36</v>
+      </c>
+      <c r="E25" t="n">
+        <v>36</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1011.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1044</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N23"/>
+  <autoFilter ref="A1:N25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10977,7 +11703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11607,7 +12333,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>1</v>
       </c>
@@ -11625,8 +12350,107 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4170</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>661.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>656</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4176</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>746.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1079</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N13"/>
+  <autoFilter ref="A1:N15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11637,7 +12461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11760,7 +12584,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>1</v>
       </c>
@@ -11778,8 +12601,107 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3599</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>582.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>466</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3604</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>596.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>641</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11790,7 +12712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11908,8 +12830,6 @@
       <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
@@ -11927,8 +12847,102 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11939,7 +12953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12048,8 +13062,6 @@
       <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
@@ -12067,8 +13079,93 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>21118</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -21,18 +21,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="company-facts" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$N$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$N$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$N$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$N$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$N$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$N$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -464,9 +464,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,6 +541,7 @@
           <t>バズ続編投入数</t>
         </is>
       </c>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3391,8 +3393,122 @@
         <v>0</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>63</v>
+      </c>
+      <c r="C57" t="n">
+        <v>183565</v>
+      </c>
+      <c r="D57" t="n">
+        <v>197</v>
+      </c>
+      <c r="E57" t="n">
+        <v>39</v>
+      </c>
+      <c r="F57" t="n">
+        <v>850</v>
+      </c>
+      <c r="G57" t="n">
+        <v>896</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.4861</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>15</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>61</v>
+      </c>
+      <c r="C58" t="n">
+        <v>183588</v>
+      </c>
+      <c r="D58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E58" t="n">
+        <v>39</v>
+      </c>
+      <c r="F58" t="n">
+        <v>818.9</v>
+      </c>
+      <c r="G58" t="n">
+        <v>879</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.5083</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>15</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N56"/>
+  <autoFilter ref="A1:O58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3403,7 +3519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3417,9 +3533,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3493,6 +3610,7 @@
           <t>バズ続編投入数</t>
         </is>
       </c>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3596,7 +3714,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>3</v>
       </c>
@@ -3614,8 +3731,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>18330</v>
+      </c>
+      <c r="D5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>686</v>
+      </c>
+      <c r="G5" t="n">
+        <v>901</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>18341</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>866.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>966</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.0163</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:O6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3626,7 +3848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3640,9 +3862,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3716,6 +3939,7 @@
           <t>バズ続編投入数</t>
         </is>
       </c>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3829,7 +4053,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>0</v>
       </c>
@@ -3847,8 +4070,113 @@
         <v>2</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>29029</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3194.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>29058</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2895.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1230</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:O6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3859,7 +4187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3873,9 +4201,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3949,6 +4278,7 @@
           <t>バズ続編投入数</t>
         </is>
       </c>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4062,7 +4392,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>1</v>
       </c>
@@ -4080,8 +4409,113 @@
         <v>2</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" t="n">
+        <v>37336</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1392.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1233</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7030999999999999</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C6" t="n">
+        <v>37405</v>
+      </c>
+      <c r="D6" t="n">
+        <v>33</v>
+      </c>
+      <c r="E6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1341.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1123</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:O6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4092,7 +4526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4106,9 +4540,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4182,6 +4617,7 @@
           <t>バズ続編投入数</t>
         </is>
       </c>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7033,8 +7469,122 @@
         <v>0</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>151</v>
+      </c>
+      <c r="C57" t="n">
+        <v>150413</v>
+      </c>
+      <c r="D57" t="n">
+        <v>175</v>
+      </c>
+      <c r="E57" t="n">
+        <v>46</v>
+      </c>
+      <c r="F57" t="n">
+        <v>764</v>
+      </c>
+      <c r="G57" t="n">
+        <v>890</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>15</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>154</v>
+      </c>
+      <c r="C58" t="n">
+        <v>150527</v>
+      </c>
+      <c r="D58" t="n">
+        <v>179</v>
+      </c>
+      <c r="E58" t="n">
+        <v>48</v>
+      </c>
+      <c r="F58" t="n">
+        <v>762.7</v>
+      </c>
+      <c r="G58" t="n">
+        <v>892</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.5528</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>15</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N56"/>
+  <autoFilter ref="A1:O58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7045,7 +7595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7059,9 +7609,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7135,6 +7686,7 @@
           <t>バズ続編投入数</t>
         </is>
       </c>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8722,7 +9274,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
         <v>9</v>
       </c>
@@ -8740,8 +9291,113 @@
         <v>2</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>15</v>
+      </c>
+      <c r="C36" t="n">
+        <v>48808</v>
+      </c>
+      <c r="D36" t="n">
+        <v>42</v>
+      </c>
+      <c r="E36" t="n">
+        <v>31</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1092.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1030</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2562</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>48814</v>
+      </c>
+      <c r="D37" t="n">
+        <v>45</v>
+      </c>
+      <c r="E37" t="n">
+        <v>33</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1047</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1010</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>9</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N35"/>
+  <autoFilter ref="A1:O37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8752,7 +9408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8766,9 +9422,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8842,6 +9499,7 @@
           <t>バズ続編投入数</t>
         </is>
       </c>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10429,7 +11087,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
         <v>15</v>
       </c>
@@ -10447,8 +11104,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>42439</v>
+      </c>
+      <c r="D36" t="n">
+        <v>42</v>
+      </c>
+      <c r="E36" t="n">
+        <v>32</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1029.7</v>
+      </c>
+      <c r="G36" t="n">
+        <v>989</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2566</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>15</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>19</v>
+      </c>
+      <c r="C37" t="n">
+        <v>42461</v>
+      </c>
+      <c r="D37" t="n">
+        <v>45</v>
+      </c>
+      <c r="E37" t="n">
+        <v>34</v>
+      </c>
+      <c r="F37" t="n">
+        <v>992.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>992</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>15</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N35"/>
+  <autoFilter ref="A1:O37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10459,7 +11221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10473,9 +11235,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10549,6 +11312,7 @@
           <t>バズ続編投入数</t>
         </is>
       </c>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11673,7 +12437,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
         <v>5</v>
       </c>
@@ -11691,8 +12454,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" t="n">
+        <v>34597</v>
+      </c>
+      <c r="D26" t="n">
+        <v>38</v>
+      </c>
+      <c r="E26" t="n">
+        <v>38</v>
+      </c>
+      <c r="F26" t="n">
+        <v>988.9</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1002</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1733</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>8</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" t="n">
+        <v>34619</v>
+      </c>
+      <c r="D27" t="n">
+        <v>41</v>
+      </c>
+      <c r="E27" t="n">
+        <v>41</v>
+      </c>
+      <c r="F27" t="n">
+        <v>967.3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>967</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1733</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>15</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N25"/>
+  <autoFilter ref="A1:O27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11703,7 +12571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11717,9 +12585,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11793,6 +12662,7 @@
           <t>バズ続編投入数</t>
         </is>
       </c>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12431,7 +13301,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
         <v>1</v>
       </c>
@@ -12449,8 +13318,113 @@
         <v>2</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4176</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" t="n">
+        <v>689.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>463</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4176</v>
+      </c>
+      <c r="D17" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" t="n">
+        <v>773.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>856</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>15</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N15"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12461,7 +13435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12475,9 +13449,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12551,6 +13526,7 @@
           <t>バズ続編投入数</t>
         </is>
       </c>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12682,7 +13658,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>5</v>
       </c>
@@ -12700,8 +13675,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3604</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>540.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>433</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8324</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3604</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" t="n">
+        <v>479.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>226</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:O6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12712,7 +13792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12726,9 +13806,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12802,6 +13883,7 @@
           <t>バズ続編投入数</t>
         </is>
       </c>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12923,7 +14005,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>0</v>
       </c>
@@ -12941,8 +14022,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:O6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12953,7 +14139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12967,9 +14153,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13043,6 +14230,7 @@
           <t>バズ続編投入数</t>
         </is>
       </c>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13146,7 +14334,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>0</v>
       </c>
@@ -13164,8 +14351,113 @@
         <v>2</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21118</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>21289</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>272</v>
+      </c>
+      <c r="G6" t="n">
+        <v>272</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:O6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -21,18 +21,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="company-facts" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3507,8 +3507,122 @@
         <v>0</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>65</v>
+      </c>
+      <c r="C59" t="n">
+        <v>183627</v>
+      </c>
+      <c r="D59" t="n">
+        <v>203</v>
+      </c>
+      <c r="E59" t="n">
+        <v>42</v>
+      </c>
+      <c r="F59" t="n">
+        <v>854</v>
+      </c>
+      <c r="G59" t="n">
+        <v>899</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>15</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>65</v>
+      </c>
+      <c r="C60" t="n">
+        <v>183658</v>
+      </c>
+      <c r="D60" t="n">
+        <v>206</v>
+      </c>
+      <c r="E60" t="n">
+        <v>45</v>
+      </c>
+      <c r="F60" t="n">
+        <v>833.7</v>
+      </c>
+      <c r="G60" t="n">
+        <v>900</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.4676</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>15</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O58"/>
+  <autoFilter ref="A1:O60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3519,7 +3633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3818,7 +3932,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>3</v>
       </c>
@@ -3836,8 +3949,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>18362</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>746.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>958</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5206</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>18369</v>
+      </c>
+      <c r="D8" t="n">
+        <v>27</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1055.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1164</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3848,7 +4066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4157,7 +4375,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>0</v>
       </c>
@@ -4175,8 +4392,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>29068</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3345.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1267</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>29094</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" t="n">
+        <v>16</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3924.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1259</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4187,7 +4509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4496,7 +4818,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>10</v>
       </c>
@@ -4514,8 +4835,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>31</v>
+      </c>
+      <c r="C7" t="n">
+        <v>37420</v>
+      </c>
+      <c r="D7" t="n">
+        <v>36</v>
+      </c>
+      <c r="E7" t="n">
+        <v>36</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1324.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1108</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C8" t="n">
+        <v>37452</v>
+      </c>
+      <c r="D8" t="n">
+        <v>39</v>
+      </c>
+      <c r="E8" t="n">
+        <v>39</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1306.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1107</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6388</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4526,7 +4952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7583,8 +8009,122 @@
         <v>0</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>156</v>
+      </c>
+      <c r="C59" t="n">
+        <v>150607</v>
+      </c>
+      <c r="D59" t="n">
+        <v>182</v>
+      </c>
+      <c r="E59" t="n">
+        <v>51</v>
+      </c>
+      <c r="F59" t="n">
+        <v>770.2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>905</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.6219</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>15</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>158</v>
+      </c>
+      <c r="C60" t="n">
+        <v>150680</v>
+      </c>
+      <c r="D60" t="n">
+        <v>185</v>
+      </c>
+      <c r="E60" t="n">
+        <v>52</v>
+      </c>
+      <c r="F60" t="n">
+        <v>772.1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>910</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.6542</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>15</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O58"/>
+  <autoFilter ref="A1:O60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7595,7 +8135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9378,7 +9918,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>9</v>
       </c>
@@ -9396,8 +9935,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>48819</v>
+      </c>
+      <c r="D38" t="n">
+        <v>48</v>
+      </c>
+      <c r="E38" t="n">
+        <v>36</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1022.3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>996</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>10</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>48826</v>
+      </c>
+      <c r="D39" t="n">
+        <v>52</v>
+      </c>
+      <c r="E39" t="n">
+        <v>40</v>
+      </c>
+      <c r="F39" t="n">
+        <v>958.9</v>
+      </c>
+      <c r="G39" t="n">
+        <v>965</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>10</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O37"/>
+  <autoFilter ref="A1:O39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9408,7 +10052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11191,7 +11835,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>15</v>
       </c>
@@ -11209,8 +11852,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>20</v>
+      </c>
+      <c r="C38" t="n">
+        <v>42480</v>
+      </c>
+      <c r="D38" t="n">
+        <v>48</v>
+      </c>
+      <c r="E38" t="n">
+        <v>37</v>
+      </c>
+      <c r="F38" t="n">
+        <v>978.7</v>
+      </c>
+      <c r="G38" t="n">
+        <v>988</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>15</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>23</v>
+      </c>
+      <c r="C39" t="n">
+        <v>42491</v>
+      </c>
+      <c r="D39" t="n">
+        <v>50</v>
+      </c>
+      <c r="E39" t="n">
+        <v>39</v>
+      </c>
+      <c r="F39" t="n">
+        <v>975.2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>988</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>15</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O37"/>
+  <autoFilter ref="A1:O39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11221,7 +11969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12541,7 +13289,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
         <v>15</v>
       </c>
@@ -12559,8 +13306,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>34622</v>
+      </c>
+      <c r="D28" t="n">
+        <v>44</v>
+      </c>
+      <c r="E28" t="n">
+        <v>44</v>
+      </c>
+      <c r="F28" t="n">
+        <v>951.3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>965</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2139</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>34629</v>
+      </c>
+      <c r="D29" t="n">
+        <v>47</v>
+      </c>
+      <c r="E29" t="n">
+        <v>47</v>
+      </c>
+      <c r="F29" t="n">
+        <v>938.9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>967</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2019</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O27"/>
+  <autoFilter ref="A1:O29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12571,7 +13423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13405,7 +14257,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>15</v>
       </c>
@@ -13423,8 +14274,104 @@
         <v>2</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4176</v>
+      </c>
+      <c r="D18" t="n">
+        <v>17</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17</v>
+      </c>
+      <c r="F18" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>916</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13435,7 +14382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13762,7 +14709,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>15</v>
       </c>
@@ -13780,8 +14726,104 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3605</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>415.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5392</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13792,7 +14834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14109,7 +15151,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>0</v>
       </c>
@@ -14127,8 +15168,104 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14139,7 +15276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14438,7 +15575,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>0</v>
       </c>
@@ -14456,8 +15592,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>21414</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>710.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>809</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>21488</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>851.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1094</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -21,18 +21,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="company-facts" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3621,8 +3621,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>68</v>
+      </c>
+      <c r="C61" t="n">
+        <v>183684</v>
+      </c>
+      <c r="D61" t="n">
+        <v>209</v>
+      </c>
+      <c r="E61" t="n">
+        <v>43</v>
+      </c>
+      <c r="F61" t="n">
+        <v>853.8</v>
+      </c>
+      <c r="G61" t="n">
+        <v>908</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>15</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O60"/>
+  <autoFilter ref="A1:O61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3633,7 +3690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4036,7 +4093,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>3</v>
       </c>
@@ -4054,8 +4110,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>18385</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1078.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1169</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O8"/>
+  <autoFilter ref="A1:O9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4066,7 +4175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4479,7 +4588,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>0</v>
       </c>
@@ -4497,8 +4605,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>29113</v>
+      </c>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3746.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1260</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O8"/>
+  <autoFilter ref="A1:O9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4509,7 +4670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4922,7 +5083,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>2</v>
       </c>
@@ -4940,8 +5100,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>32</v>
+      </c>
+      <c r="C9" t="n">
+        <v>37494</v>
+      </c>
+      <c r="D9" t="n">
+        <v>42</v>
+      </c>
+      <c r="E9" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1281.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1060</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.6574</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O8"/>
+  <autoFilter ref="A1:O9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4952,7 +5165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8123,8 +8336,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>161</v>
+      </c>
+      <c r="C61" t="n">
+        <v>150735</v>
+      </c>
+      <c r="D61" t="n">
+        <v>188</v>
+      </c>
+      <c r="E61" t="n">
+        <v>51</v>
+      </c>
+      <c r="F61" t="n">
+        <v>748.1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>912</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.7020999999999999</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>15</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O60"/>
+  <autoFilter ref="A1:O61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8135,7 +8405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10022,7 +10292,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
         <v>10</v>
       </c>
@@ -10040,8 +10309,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>48828</v>
+      </c>
+      <c r="D40" t="n">
+        <v>55</v>
+      </c>
+      <c r="E40" t="n">
+        <v>40</v>
+      </c>
+      <c r="F40" t="n">
+        <v>932.2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>924</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.2738</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O39"/>
+  <autoFilter ref="A1:O40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10052,7 +10374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11939,7 +12261,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
         <v>15</v>
       </c>
@@ -11957,8 +12278,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>26</v>
+      </c>
+      <c r="C40" t="n">
+        <v>42501</v>
+      </c>
+      <c r="D40" t="n">
+        <v>53</v>
+      </c>
+      <c r="E40" t="n">
+        <v>39</v>
+      </c>
+      <c r="F40" t="n">
+        <v>918.8</v>
+      </c>
+      <c r="G40" t="n">
+        <v>985</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>8</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O39"/>
+  <autoFilter ref="A1:O40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11969,7 +12343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13393,7 +13767,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
         <v>6</v>
       </c>
@@ -13411,8 +13784,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>34631</v>
+      </c>
+      <c r="D30" t="n">
+        <v>50</v>
+      </c>
+      <c r="E30" t="n">
+        <v>49</v>
+      </c>
+      <c r="F30" t="n">
+        <v>906.3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>963</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O29"/>
+  <autoFilter ref="A1:O30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13423,7 +13849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14352,7 +14778,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -14370,8 +14795,52 @@
         <v>1</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
+  <autoFilter ref="A1:O20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14382,7 +14851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14804,7 +15273,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>0</v>
       </c>
@@ -14822,8 +15290,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O8"/>
+  <autoFilter ref="A1:O9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14834,7 +15346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15246,7 +15758,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>0</v>
       </c>
@@ -15264,8 +15775,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O8"/>
+  <autoFilter ref="A1:O9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15276,7 +15831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15679,7 +16234,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>0</v>
       </c>
@@ -15697,8 +16251,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>21549</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>854.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1114</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O8"/>
+  <autoFilter ref="A1:O9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -21,18 +21,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="company-facts" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3678,8 +3678,56 @@
         <v>0</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>15</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O61"/>
+  <autoFilter ref="A1:O62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3690,7 +3738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4145,7 +4193,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>3</v>
       </c>
@@ -4163,8 +4210,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O9"/>
+  <autoFilter ref="A1:O10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4175,7 +4266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4640,7 +4731,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -4658,8 +4748,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O9"/>
+  <autoFilter ref="A1:O10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4670,7 +4804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5135,7 +5269,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -5153,8 +5286,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O9"/>
+  <autoFilter ref="A1:O10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5165,7 +5342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8393,8 +8570,56 @@
         <v>0</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>15</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O61"/>
+  <autoFilter ref="A1:O62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8405,7 +8630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10344,7 +10569,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>1</v>
       </c>
@@ -10362,8 +10586,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O40"/>
+  <autoFilter ref="A1:O41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10374,7 +10642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12313,7 +12581,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>8</v>
       </c>
@@ -12331,8 +12598,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>8</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O40"/>
+  <autoFilter ref="A1:O41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12343,7 +12654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13819,7 +14130,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
         <v>1</v>
       </c>
@@ -13837,8 +14147,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O30"/>
+  <autoFilter ref="A1:O31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13849,7 +14203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14821,7 +15175,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>0</v>
       </c>
@@ -14839,8 +15192,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O20"/>
+  <autoFilter ref="A1:O21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14851,7 +15248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15316,7 +15713,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -15334,8 +15730,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O9"/>
+  <autoFilter ref="A1:O10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15346,7 +15786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15801,7 +16241,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -15819,8 +16258,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O9"/>
+  <autoFilter ref="A1:O10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15831,7 +16314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16286,7 +16769,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -16304,8 +16786,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O9"/>
+  <autoFilter ref="A1:O10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -21,18 +21,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="company-facts" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3726,8 +3726,56 @@
         <v>0</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>15</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O62"/>
+  <autoFilter ref="A1:O63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3738,7 +3786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4236,7 +4284,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>3</v>
       </c>
@@ -4254,8 +4301,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:O11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4266,7 +4357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4774,7 +4865,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -4792,8 +4882,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:O11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4804,7 +4938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5312,7 +5446,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -5330,8 +5463,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:O11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5342,7 +5519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8618,8 +8795,56 @@
         <v>0</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>15</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O62"/>
+  <autoFilter ref="A1:O63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8630,7 +8855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10612,7 +10837,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>1</v>
       </c>
@@ -10630,8 +10854,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
+  <autoFilter ref="A1:O42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10642,7 +10910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12624,7 +12892,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>8</v>
       </c>
@@ -12642,8 +12909,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>8</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
+  <autoFilter ref="A1:O42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12654,7 +12965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14173,7 +14484,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>1</v>
       </c>
@@ -14191,8 +14501,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O31"/>
+  <autoFilter ref="A1:O32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14203,7 +14557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15218,7 +15572,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
         <v>0</v>
       </c>
@@ -15236,8 +15589,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O21"/>
+  <autoFilter ref="A1:O22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15248,7 +15645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15756,7 +16153,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -15774,8 +16170,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:O11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15786,7 +16226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16284,7 +16724,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -16302,8 +16741,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:O11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16314,7 +16797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16812,7 +17295,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -16830,8 +17312,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:O11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -21,18 +21,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="company-facts" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3774,8 +3774,56 @@
         <v>0</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>15</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O63"/>
+  <autoFilter ref="A1:O64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3786,7 +3834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4327,7 +4375,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>3</v>
       </c>
@@ -4345,8 +4392,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4357,7 +4448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4908,7 +4999,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -4926,8 +5016,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4938,7 +5072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5489,7 +5623,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -5507,8 +5640,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5519,7 +5696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8843,8 +9020,56 @@
         <v>0</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>15</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O63"/>
+  <autoFilter ref="A1:O64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8855,7 +9080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10880,7 +11105,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>1</v>
       </c>
@@ -10898,8 +11122,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O42"/>
+  <autoFilter ref="A1:O43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10910,7 +11178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12935,7 +13203,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>8</v>
       </c>
@@ -12953,8 +13220,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>6</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O42"/>
+  <autoFilter ref="A1:O43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12965,7 +13276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14527,7 +14838,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
         <v>1</v>
       </c>
@@ -14545,8 +14855,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O32"/>
+  <autoFilter ref="A1:O33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14557,7 +14911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15615,7 +15969,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
         <v>0</v>
       </c>
@@ -15633,8 +15986,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O22"/>
+  <autoFilter ref="A1:O23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15645,7 +16042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16196,7 +16593,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -16214,8 +16610,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16226,7 +16666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16767,7 +17207,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -16785,8 +17224,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16797,7 +17280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17338,7 +17821,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -17356,8 +17838,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -22,19 +22,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="socio-rx" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'socio-rx'!$A$1:$O$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'socio-rx'!$A$1:$O$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3881,8 +3881,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>72</v>
+      </c>
+      <c r="C66" t="n">
+        <v>200318</v>
+      </c>
+      <c r="D66" t="n">
+        <v>215</v>
+      </c>
+      <c r="E66" t="n">
+        <v>41</v>
+      </c>
+      <c r="F66" t="n">
+        <v>877.8</v>
+      </c>
+      <c r="G66" t="n">
+        <v>951</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.7007</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>15</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O65"/>
+  <autoFilter ref="A1:O66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3893,7 +3950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4520,7 +4577,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>3</v>
       </c>
@@ -4538,8 +4594,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O13"/>
+  <autoFilter ref="A1:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4550,7 +4650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5187,7 +5287,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -5205,8 +5304,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O13"/>
+  <autoFilter ref="A1:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5217,7 +5360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5863,7 +6006,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -5881,8 +6023,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>36</v>
+      </c>
+      <c r="C14" t="n">
+        <v>57541</v>
+      </c>
+      <c r="D14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" t="n">
+        <v>44</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1252.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1055</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6167</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O13"/>
+  <autoFilter ref="A1:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5893,7 +6088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6025,7 +6220,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>0</v>
       </c>
@@ -6043,8 +6237,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1070</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>693</v>
+      </c>
+      <c r="G3" t="n">
+        <v>693</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O2"/>
+  <autoFilter ref="A1:O3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6055,7 +6302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9484,8 +9731,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>162</v>
+      </c>
+      <c r="C66" t="n">
+        <v>166728</v>
+      </c>
+      <c r="D66" t="n">
+        <v>194</v>
+      </c>
+      <c r="E66" t="n">
+        <v>50</v>
+      </c>
+      <c r="F66" t="n">
+        <v>729.2</v>
+      </c>
+      <c r="G66" t="n">
+        <v>913</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.8339</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>15</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O65"/>
+  <autoFilter ref="A1:O66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9496,7 +9800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11607,7 +11911,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
         <v>0</v>
       </c>
@@ -11625,8 +11928,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O44"/>
+  <autoFilter ref="A1:O45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11637,7 +11984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13757,7 +14104,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
         <v>7</v>
       </c>
@@ -13775,8 +14121,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>27</v>
+      </c>
+      <c r="C45" t="n">
+        <v>55870</v>
+      </c>
+      <c r="D45" t="n">
+        <v>58</v>
+      </c>
+      <c r="E45" t="n">
+        <v>38</v>
+      </c>
+      <c r="F45" t="n">
+        <v>729.8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>806</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.7514999999999999</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>7</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O44"/>
+  <autoFilter ref="A1:O45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13787,7 +14186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15444,7 +15843,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
         <v>0</v>
       </c>
@@ -15462,8 +15860,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" t="n">
+        <v>47451</v>
+      </c>
+      <c r="D35" t="n">
+        <v>51</v>
+      </c>
+      <c r="E35" t="n">
+        <v>44</v>
+      </c>
+      <c r="F35" t="n">
+        <v>864.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>944</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O34"/>
+  <autoFilter ref="A1:O35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15474,7 +15925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16618,7 +17069,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>0</v>
       </c>
@@ -16636,8 +17086,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O24"/>
+  <autoFilter ref="A1:O25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16648,7 +17142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17285,7 +17779,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -17303,8 +17796,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O13"/>
+  <autoFilter ref="A1:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17315,7 +17852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17942,7 +18479,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -17960,8 +18496,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O13"/>
+  <autoFilter ref="A1:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17972,7 +18552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18599,7 +19179,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -18617,8 +19196,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O13"/>
+  <autoFilter ref="A1:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -22,19 +22,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="socio-rx" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'socio-rx'!$A$1:$O$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'socio-rx'!$A$1:$O$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3938,8 +3938,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>74</v>
+      </c>
+      <c r="C67" t="n">
+        <v>203374</v>
+      </c>
+      <c r="D67" t="n">
+        <v>218</v>
+      </c>
+      <c r="E67" t="n">
+        <v>44</v>
+      </c>
+      <c r="F67" t="n">
+        <v>879</v>
+      </c>
+      <c r="G67" t="n">
+        <v>939</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.7009</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>15</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O66"/>
+  <autoFilter ref="A1:O67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3950,7 +4007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4620,7 +4677,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>3</v>
       </c>
@@ -4638,8 +4694,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O14"/>
+  <autoFilter ref="A1:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4650,7 +4750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5330,7 +5430,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>0</v>
       </c>
@@ -5348,8 +5447,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O14"/>
+  <autoFilter ref="A1:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5360,7 +5503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6058,7 +6201,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>0</v>
       </c>
@@ -6076,8 +6218,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>39</v>
+      </c>
+      <c r="C15" t="n">
+        <v>60575</v>
+      </c>
+      <c r="D15" t="n">
+        <v>54</v>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1220.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1055</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6162</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O14"/>
+  <autoFilter ref="A1:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6088,7 +6283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6272,7 +6467,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>0</v>
       </c>
@@ -6290,8 +6484,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1070</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>470</v>
+      </c>
+      <c r="G4" t="n">
+        <v>379</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O3"/>
+  <autoFilter ref="A1:O4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6302,7 +6549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9788,8 +10035,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>164</v>
+      </c>
+      <c r="C67" t="n">
+        <v>169070</v>
+      </c>
+      <c r="D67" t="n">
+        <v>195</v>
+      </c>
+      <c r="E67" t="n">
+        <v>52</v>
+      </c>
+      <c r="F67" t="n">
+        <v>737.7</v>
+      </c>
+      <c r="G67" t="n">
+        <v>913</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.8083</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>15</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O66"/>
+  <autoFilter ref="A1:O67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9800,7 +10104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11954,7 +12258,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
         <v>0</v>
       </c>
@@ -11972,8 +12275,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O45"/>
+  <autoFilter ref="A1:O46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11984,7 +12331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14156,7 +14503,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
         <v>7</v>
       </c>
@@ -14174,8 +14520,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>28</v>
+      </c>
+      <c r="C46" t="n">
+        <v>57099</v>
+      </c>
+      <c r="D46" t="n">
+        <v>61</v>
+      </c>
+      <c r="E46" t="n">
+        <v>41</v>
+      </c>
+      <c r="F46" t="n">
+        <v>707.1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>789</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.7514999999999999</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>7</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O45"/>
+  <autoFilter ref="A1:O46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14186,7 +14585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15895,7 +16294,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>0</v>
       </c>
@@ -15913,8 +16311,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" t="n">
+        <v>47453</v>
+      </c>
+      <c r="D36" t="n">
+        <v>51</v>
+      </c>
+      <c r="E36" t="n">
+        <v>43</v>
+      </c>
+      <c r="F36" t="n">
+        <v>853</v>
+      </c>
+      <c r="G36" t="n">
+        <v>941</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O35"/>
+  <autoFilter ref="A1:O36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15925,7 +16376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17112,7 +17563,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>0</v>
       </c>
@@ -17130,8 +17580,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O25"/>
+  <autoFilter ref="A1:O26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17142,7 +17636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17822,7 +18316,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>0</v>
       </c>
@@ -17840,8 +18333,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O14"/>
+  <autoFilter ref="A1:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17852,7 +18389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18522,7 +19059,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>0</v>
       </c>
@@ -18540,8 +19076,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O14"/>
+  <autoFilter ref="A1:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18552,7 +19132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19222,7 +19802,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>0</v>
       </c>
@@ -19240,8 +19819,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O14"/>
+  <autoFilter ref="A1:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -22,19 +22,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="socio-rx" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'socio-rx'!$A$1:$O$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'socio-rx'!$A$1:$O$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3995,8 +3995,122 @@
         <v>0</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>74</v>
+      </c>
+      <c r="C68" t="n">
+        <v>207053</v>
+      </c>
+      <c r="D68" t="n">
+        <v>220</v>
+      </c>
+      <c r="E68" t="n">
+        <v>45</v>
+      </c>
+      <c r="F68" t="n">
+        <v>912</v>
+      </c>
+      <c r="G68" t="n">
+        <v>952</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.6679</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>15</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>75</v>
+      </c>
+      <c r="C69" t="n">
+        <v>209387</v>
+      </c>
+      <c r="D69" t="n">
+        <v>224</v>
+      </c>
+      <c r="E69" t="n">
+        <v>48</v>
+      </c>
+      <c r="F69" t="n">
+        <v>916.7</v>
+      </c>
+      <c r="G69" t="n">
+        <v>953</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.6617</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>15</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O67"/>
+  <autoFilter ref="A1:O69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4007,7 +4121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4720,7 +4834,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>3</v>
       </c>
@@ -4738,8 +4851,95 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O15"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4750,7 +4950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5473,7 +5673,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>0</v>
       </c>
@@ -5491,8 +5690,95 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O15"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5503,7 +5789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6253,7 +6539,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>0</v>
       </c>
@@ -6271,8 +6556,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>42</v>
+      </c>
+      <c r="C16" t="n">
+        <v>65778</v>
+      </c>
+      <c r="D16" t="n">
+        <v>57</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1210.8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1057</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6012999999999999</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>42</v>
+      </c>
+      <c r="C17" t="n">
+        <v>68204</v>
+      </c>
+      <c r="D17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E17" t="n">
+        <v>52</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1233.9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1067</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5735</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O15"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6283,7 +6673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6519,7 +6909,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -6537,8 +6926,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1403</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>649.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>624</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3165</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>755.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>612</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O4"/>
+  <autoFilter ref="A1:O6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6549,7 +7043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10092,8 +10586,122 @@
         <v>0</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>166</v>
+      </c>
+      <c r="C68" t="n">
+        <v>171998</v>
+      </c>
+      <c r="D68" t="n">
+        <v>198</v>
+      </c>
+      <c r="E68" t="n">
+        <v>53</v>
+      </c>
+      <c r="F68" t="n">
+        <v>740</v>
+      </c>
+      <c r="G68" t="n">
+        <v>914</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.8245</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>財団組織・職員</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>15</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>167</v>
+      </c>
+      <c r="C69" t="n">
+        <v>174886</v>
+      </c>
+      <c r="D69" t="n">
+        <v>201</v>
+      </c>
+      <c r="E69" t="n">
+        <v>55</v>
+      </c>
+      <c r="F69" t="n">
+        <v>739.2</v>
+      </c>
+      <c r="G69" t="n">
+        <v>918</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.7877</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>財団組織・職員</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>15</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O67"/>
+  <autoFilter ref="A1:O69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10104,7 +10712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12301,7 +12909,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>0</v>
       </c>
@@ -12319,8 +12926,95 @@
         <v>0</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O46"/>
+  <autoFilter ref="A1:O48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12331,7 +13025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14555,7 +15249,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>7</v>
       </c>
@@ -14573,8 +15266,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>29</v>
+      </c>
+      <c r="C47" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D47" t="n">
+        <v>63</v>
+      </c>
+      <c r="E47" t="n">
+        <v>43</v>
+      </c>
+      <c r="F47" t="n">
+        <v>644.6</v>
+      </c>
+      <c r="G47" t="n">
+        <v>752</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.7606000000000001</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>7</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>29</v>
+      </c>
+      <c r="C48" t="n">
+        <v>59410</v>
+      </c>
+      <c r="D48" t="n">
+        <v>66</v>
+      </c>
+      <c r="E48" t="n">
+        <v>45</v>
+      </c>
+      <c r="F48" t="n">
+        <v>600.7</v>
+      </c>
+      <c r="G48" t="n">
+        <v>664</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.7393</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>7</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O46"/>
+  <autoFilter ref="A1:O48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14585,7 +15383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16346,7 +17144,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>0</v>
       </c>
@@ -16364,8 +17161,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>9</v>
+      </c>
+      <c r="C37" t="n">
+        <v>47449</v>
+      </c>
+      <c r="D37" t="n">
+        <v>51</v>
+      </c>
+      <c r="E37" t="n">
+        <v>38</v>
+      </c>
+      <c r="F37" t="n">
+        <v>866.4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>934</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1822</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>9</v>
+      </c>
+      <c r="C38" t="n">
+        <v>47449</v>
+      </c>
+      <c r="D38" t="n">
+        <v>51</v>
+      </c>
+      <c r="E38" t="n">
+        <v>36</v>
+      </c>
+      <c r="F38" t="n">
+        <v>863.2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>934</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O36"/>
+  <autoFilter ref="A1:O38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16376,7 +17278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17606,7 +18508,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>0</v>
       </c>
@@ -17624,8 +18525,95 @@
         <v>0</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O26"/>
+  <autoFilter ref="A1:O28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17636,7 +18624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18359,7 +19347,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>0</v>
       </c>
@@ -18377,8 +19364,95 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O15"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18389,7 +19463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19102,7 +20176,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>0</v>
       </c>
@@ -19120,8 +20193,95 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O15"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19132,7 +20292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19845,7 +21005,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>0</v>
       </c>
@@ -19863,8 +21022,95 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O15"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -22,19 +22,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="socio-rx" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'socio-rx'!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'socio-rx'!$A$1:$O$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4109,8 +4109,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>75</v>
+      </c>
+      <c r="C70" t="n">
+        <v>210799</v>
+      </c>
+      <c r="D70" t="n">
+        <v>227</v>
+      </c>
+      <c r="E70" t="n">
+        <v>50</v>
+      </c>
+      <c r="F70" t="n">
+        <v>916.9</v>
+      </c>
+      <c r="G70" t="n">
+        <v>950</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>15</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O69"/>
+  <autoFilter ref="A1:O70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4121,7 +4178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4920,7 +4977,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>3</v>
       </c>
@@ -4938,8 +4994,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4950,7 +5050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5759,7 +5859,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>0</v>
       </c>
@@ -5777,8 +5876,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5789,7 +5932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6643,7 +6786,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>0</v>
       </c>
@@ -6661,8 +6803,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>43</v>
+      </c>
+      <c r="C18" t="n">
+        <v>68318</v>
+      </c>
+      <c r="D18" t="n">
+        <v>64</v>
+      </c>
+      <c r="E18" t="n">
+        <v>55</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1241.8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1066</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5591</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6673,7 +6868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7013,7 +7208,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>0</v>
       </c>
@@ -7031,8 +7225,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3167</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>832.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>801</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7043,7 +7290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10700,8 +10947,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>167</v>
+      </c>
+      <c r="C70" t="n">
+        <v>175530</v>
+      </c>
+      <c r="D70" t="n">
+        <v>204</v>
+      </c>
+      <c r="E70" t="n">
+        <v>57</v>
+      </c>
+      <c r="F70" t="n">
+        <v>736.6</v>
+      </c>
+      <c r="G70" t="n">
+        <v>942</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.7624</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>財団組織・職員</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>15</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O69"/>
+  <autoFilter ref="A1:O70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10712,7 +11016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12995,7 +13299,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
         <v>0</v>
       </c>
@@ -13013,8 +13316,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O48"/>
+  <autoFilter ref="A1:O49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13025,7 +13372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15353,7 +15700,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
         <v>7</v>
       </c>
@@ -15371,8 +15717,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>29</v>
+      </c>
+      <c r="C49" t="n">
+        <v>59433</v>
+      </c>
+      <c r="D49" t="n">
+        <v>69</v>
+      </c>
+      <c r="E49" t="n">
+        <v>47</v>
+      </c>
+      <c r="F49" t="n">
+        <v>587.7</v>
+      </c>
+      <c r="G49" t="n">
+        <v>612</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.7344000000000001</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>7</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O48"/>
+  <autoFilter ref="A1:O49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15383,7 +15782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17248,7 +17647,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
         <v>0</v>
       </c>
@@ -17266,8 +17664,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>11</v>
+      </c>
+      <c r="C39" t="n">
+        <v>47449</v>
+      </c>
+      <c r="D39" t="n">
+        <v>53</v>
+      </c>
+      <c r="E39" t="n">
+        <v>36</v>
+      </c>
+      <c r="F39" t="n">
+        <v>834.7</v>
+      </c>
+      <c r="G39" t="n">
+        <v>917</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O38"/>
+  <autoFilter ref="A1:O39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17278,7 +17729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18594,7 +19045,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>0</v>
       </c>
@@ -18612,8 +19062,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O28"/>
+  <autoFilter ref="A1:O29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18624,7 +19118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19433,7 +19927,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>0</v>
       </c>
@@ -19451,8 +19944,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19463,7 +20000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20262,7 +20799,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>0</v>
       </c>
@@ -20280,8 +20816,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20292,7 +20872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21091,7 +21671,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>0</v>
       </c>
@@ -21109,8 +21688,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -22,19 +22,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="socio-rx" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'socio-rx'!$A$1:$O$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'socio-rx'!$A$1:$O$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4166,8 +4166,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>76</v>
+      </c>
+      <c r="C71" t="n">
+        <v>216507</v>
+      </c>
+      <c r="D71" t="n">
+        <v>230</v>
+      </c>
+      <c r="E71" t="n">
+        <v>52</v>
+      </c>
+      <c r="F71" t="n">
+        <v>905.5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>935</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>15</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O70"/>
+  <autoFilter ref="A1:O71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4178,7 +4235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5020,7 +5077,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>3</v>
       </c>
@@ -5038,8 +5094,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O18"/>
+  <autoFilter ref="A1:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5050,7 +5150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5902,7 +6002,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>0</v>
       </c>
@@ -5920,8 +6019,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O18"/>
+  <autoFilter ref="A1:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5932,7 +6075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6838,7 +6981,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>0</v>
       </c>
@@ -6856,8 +6998,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>44</v>
+      </c>
+      <c r="C19" t="n">
+        <v>75882</v>
+      </c>
+      <c r="D19" t="n">
+        <v>68</v>
+      </c>
+      <c r="E19" t="n">
+        <v>58</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1141.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1058</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5419</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O18"/>
+  <autoFilter ref="A1:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6868,7 +7063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7260,7 +7455,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>0</v>
       </c>
@@ -7278,8 +7472,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5626</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>787.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1025</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O7"/>
+  <autoFilter ref="A1:O8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7290,7 +7537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11004,8 +11251,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>170</v>
+      </c>
+      <c r="C71" t="n">
+        <v>178636</v>
+      </c>
+      <c r="D71" t="n">
+        <v>207</v>
+      </c>
+      <c r="E71" t="n">
+        <v>59</v>
+      </c>
+      <c r="F71" t="n">
+        <v>725.3</v>
+      </c>
+      <c r="G71" t="n">
+        <v>915</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.7955</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>財団組織・職員</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>15</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O70"/>
+  <autoFilter ref="A1:O71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11016,7 +11320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13342,7 +13646,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
         <v>0</v>
       </c>
@@ -13360,8 +13663,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O49"/>
+  <autoFilter ref="A1:O50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13372,7 +13719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15752,7 +16099,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
         <v>7</v>
       </c>
@@ -15770,8 +16116,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>31</v>
+      </c>
+      <c r="C50" t="n">
+        <v>62689</v>
+      </c>
+      <c r="D50" t="n">
+        <v>72</v>
+      </c>
+      <c r="E50" t="n">
+        <v>49</v>
+      </c>
+      <c r="F50" t="n">
+        <v>601.4</v>
+      </c>
+      <c r="G50" t="n">
+        <v>721</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.7494</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>7</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O49"/>
+  <autoFilter ref="A1:O50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15782,7 +16181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17699,7 +18098,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
         <v>0</v>
       </c>
@@ -17717,8 +18115,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>11</v>
+      </c>
+      <c r="C40" t="n">
+        <v>49087</v>
+      </c>
+      <c r="D40" t="n">
+        <v>54</v>
+      </c>
+      <c r="E40" t="n">
+        <v>35</v>
+      </c>
+      <c r="F40" t="n">
+        <v>847.1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>941</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O39"/>
+  <autoFilter ref="A1:O40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17729,7 +18180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19088,7 +19539,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
         <v>0</v>
       </c>
@@ -19106,8 +19556,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O29"/>
+  <autoFilter ref="A1:O30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19118,7 +19612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19970,7 +20464,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>0</v>
       </c>
@@ -19988,8 +20481,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O18"/>
+  <autoFilter ref="A1:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20000,7 +20537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20842,7 +21379,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>0</v>
       </c>
@@ -20860,8 +21396,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O18"/>
+  <autoFilter ref="A1:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20872,7 +21452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21714,7 +22294,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>0</v>
       </c>
@@ -21732,8 +22311,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O18"/>
+  <autoFilter ref="A1:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -22,19 +22,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="socio-rx" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'socio-rx'!$A$1:$O$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$O$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$O$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$O$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$O$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$O$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'akashic-librarian'!$A$1:$O$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'clip-animal'!$A$1:$O$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'clip-fukada'!$A$1:$O$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'clip-kaneko'!$A$1:$O$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'clip-lab'!$A$1:$O$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'company-facts'!$A$1:$O$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'socio-rx'!$A$1:$O$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4223,8 +4223,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>74</v>
+      </c>
+      <c r="C72" t="n">
+        <v>216065</v>
+      </c>
+      <c r="D72" t="n">
+        <v>233</v>
+      </c>
+      <c r="E72" t="n">
+        <v>53</v>
+      </c>
+      <c r="F72" t="n">
+        <v>905</v>
+      </c>
+      <c r="G72" t="n">
+        <v>929</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>15</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O71"/>
+  <autoFilter ref="A1:O72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4235,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5120,7 +5177,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>3</v>
       </c>
@@ -5138,8 +5194,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
+  <autoFilter ref="A1:O20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5150,7 +5250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6045,7 +6145,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -6063,8 +6162,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
+  <autoFilter ref="A1:O20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6075,7 +6218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7033,7 +7176,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -7051,8 +7193,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>44</v>
+      </c>
+      <c r="C20" t="n">
+        <v>75449</v>
+      </c>
+      <c r="D20" t="n">
+        <v>72</v>
+      </c>
+      <c r="E20" t="n">
+        <v>60</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1142.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1045</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5205</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
+  <autoFilter ref="A1:O20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7063,7 +7258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7507,7 +7702,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>0</v>
       </c>
@@ -7525,8 +7719,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>660.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>705</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O8"/>
+  <autoFilter ref="A1:O9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7537,7 +7784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11308,8 +11555,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>169</v>
+      </c>
+      <c r="C72" t="n">
+        <v>178325</v>
+      </c>
+      <c r="D72" t="n">
+        <v>208</v>
+      </c>
+      <c r="E72" t="n">
+        <v>59</v>
+      </c>
+      <c r="F72" t="n">
+        <v>726.2</v>
+      </c>
+      <c r="G72" t="n">
+        <v>912</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.8054</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>財団組織・職員</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>15</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O71"/>
+  <autoFilter ref="A1:O72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11320,7 +11624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13689,7 +13993,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
         <v>0</v>
       </c>
@@ -13707,8 +14010,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>15</v>
+      </c>
+      <c r="C51" t="n">
+        <v>62017</v>
+      </c>
+      <c r="D51" t="n">
+        <v>56</v>
+      </c>
+      <c r="E51" t="n">
+        <v>29</v>
+      </c>
+      <c r="F51" t="n">
+        <v>754</v>
+      </c>
+      <c r="G51" t="n">
+        <v>866</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.2287</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O50"/>
+  <autoFilter ref="A1:O51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13719,7 +14075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16151,7 +16507,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
         <v>7</v>
       </c>
@@ -16169,8 +16524,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>28</v>
+      </c>
+      <c r="C51" t="n">
+        <v>62575</v>
+      </c>
+      <c r="D51" t="n">
+        <v>75</v>
+      </c>
+      <c r="E51" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" t="n">
+        <v>596.4</v>
+      </c>
+      <c r="G51" t="n">
+        <v>769</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.7401</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="n">
+        <v>7</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O50"/>
+  <autoFilter ref="A1:O51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16181,7 +16589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18150,7 +18558,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>0</v>
       </c>
@@ -18168,8 +18575,61 @@
         <v>0</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>11</v>
+      </c>
+      <c r="C41" t="n">
+        <v>49563</v>
+      </c>
+      <c r="D41" t="n">
+        <v>55</v>
+      </c>
+      <c r="E41" t="n">
+        <v>33</v>
+      </c>
+      <c r="F41" t="n">
+        <v>823.2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>928</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1939</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O40"/>
+  <autoFilter ref="A1:O41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18180,7 +18640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19582,7 +20042,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
         <v>0</v>
       </c>
@@ -19600,8 +20059,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O30"/>
+  <autoFilter ref="A1:O31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19612,7 +20115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20507,7 +21010,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -20525,8 +21027,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
+  <autoFilter ref="A1:O20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20537,7 +21083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21422,7 +21968,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -21440,8 +21985,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
+  <autoFilter ref="A1:O20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21452,7 +22041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22337,7 +22926,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -22355,8 +22943,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
+  <autoFilter ref="A1:O20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>